--- a/source/OPERATIONS/TP_Europe_Travel_Master_Tracker_v1.2.xlsx
+++ b/source/OPERATIONS/TP_Europe_Travel_Master_Tracker_v1.2.xlsx
@@ -8080,7 +8080,7 @@
       </c>
       <c r="D8" s="100" t="inlineStr">
         <is>
-          <t>Gordes 숙소 2박</t>
+          <t>Gordes 숙소 1박 — Rte des Moines</t>
         </is>
       </c>
       <c r="E8" s="119" t="n">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="H8" s="100" t="inlineStr">
         <is>
-          <t>미예약</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="I8" s="119" t="n">
@@ -8113,7 +8113,11 @@
       <c r="N8" s="120" t="n"/>
       <c r="O8" s="100" t="n"/>
       <c r="P8" s="100" t="n"/>
-      <c r="Q8" s="100" t="n"/>
+      <c r="Q8" s="100" t="inlineStr">
+        <is>
+          <t>104 Rte des Moines, 84220 Gordes, France</t>
+        </is>
+      </c>
       <c r="R8" s="100" t="n"/>
       <c r="S8" s="100" t="inlineStr">
         <is>
@@ -8130,7 +8134,7 @@
       </c>
       <c r="V8" s="63" t="inlineStr">
         <is>
-          <t>Gordes 2박 숙소 후보 확정 필요 (RS01)</t>
+          <t>2026-09-16 실제 예약 반영 · 체크인 목표 16:00</t>
         </is>
       </c>
     </row>
@@ -8152,11 +8156,11 @@
       </c>
       <c r="D9" s="100" t="inlineStr">
         <is>
-          <t>Avignon 숙소 4박</t>
+          <t>Avignon 숙소 5박 — Rue d'Annanelle</t>
         </is>
       </c>
       <c r="E9" s="119" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="F9" s="100" t="n"/>
       <c r="G9" s="100" t="inlineStr">
@@ -8166,7 +8170,7 @@
       </c>
       <c r="H9" s="100" t="inlineStr">
         <is>
-          <t>미예약</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="I9" s="119" t="n">
@@ -8185,7 +8189,11 @@
       <c r="N9" s="120" t="n"/>
       <c r="O9" s="100" t="n"/>
       <c r="P9" s="100" t="n"/>
-      <c r="Q9" s="100" t="n"/>
+      <c r="Q9" s="100" t="inlineStr">
+        <is>
+          <t>10 Rue d'Annanelle, 84000 Avignon, France</t>
+        </is>
+      </c>
       <c r="R9" s="100" t="n"/>
       <c r="S9" s="100" t="inlineStr">
         <is>
@@ -8202,7 +8210,7 @@
       </c>
       <c r="V9" s="63" t="inlineStr">
         <is>
-          <t>Avignon 4박 숙소 후보 확정 필요 (RS01)</t>
+          <t>2026-09-16 실제 예약 반영 · 9/15 체크인 ~ 9/20 체크아웃</t>
         </is>
       </c>
     </row>
@@ -11721,19 +11729,19 @@
         <v>46279</v>
       </c>
       <c r="C9" s="116" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>재확인</t>
+          <t>예약완료</t>
         </is>
       </c>
       <c r="F9" s="100" t="inlineStr">
         <is>
-          <t>Gordes 및 루베롱 북부 권역 (후보 미정)</t>
+          <t>Gordes · Route des Moines 권역 (Sénanque 방향 진입로)</t>
         </is>
       </c>
       <c r="G9" s="100" t="inlineStr">
@@ -11746,7 +11754,11 @@
       <c r="J9" s="120" t="n"/>
       <c r="K9" s="119" t="str"/>
       <c r="L9" s="100" t="str"/>
-      <c r="M9" s="100" t="str"/>
+      <c r="M9" s="100" t="inlineStr">
+        <is>
+          <t>104 Rte des Moines, 84220 Gordes, France</t>
+        </is>
+      </c>
       <c r="N9" s="100" t="str"/>
       <c r="O9" s="100" t="inlineStr">
         <is>
@@ -11771,7 +11783,7 @@
       <c r="S9" s="100" t="str"/>
       <c r="T9" s="63" t="inlineStr">
         <is>
-          <t>RS01: 9/14~9/16으로 변경 · 후보 미정</t>
+          <t>2026-09-16 실제 예약 반영 — 1박(9/14~9/15) 확정 · 결혼기념일 저녁 La Trinquette(9/14)</t>
         </is>
       </c>
     </row>
@@ -11782,22 +11794,22 @@
         </is>
       </c>
       <c r="B10" s="116" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="C10" s="116" t="n">
         <v>46285</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>재확인</t>
+          <t>예약완료</t>
         </is>
       </c>
       <c r="F10" s="100" t="inlineStr">
         <is>
-          <t>성벽 안(intra-muros) 도보 생활권 · La Terrasse du Clocher 등</t>
+          <t>성벽 안(intra-muros) Joseph Vernet 권역 · Rue d'Annanelle</t>
         </is>
       </c>
       <c r="G10" s="100" t="inlineStr">
@@ -11810,7 +11822,11 @@
       <c r="J10" s="120" t="n"/>
       <c r="K10" s="119" t="str"/>
       <c r="L10" s="100" t="str"/>
-      <c r="M10" s="100" t="str"/>
+      <c r="M10" s="100" t="inlineStr">
+        <is>
+          <t>10 Rue d'Annanelle, 84000 Avignon, France</t>
+        </is>
+      </c>
       <c r="N10" s="100" t="str"/>
       <c r="O10" s="100" t="inlineStr">
         <is>
@@ -11835,7 +11851,7 @@
       <c r="S10" s="100" t="str"/>
       <c r="T10" s="63" t="inlineStr">
         <is>
-          <t>RS01: 4박으로 축소 (9/16~9/20) · 후보 미정</t>
+          <t>2026-09-16 실제 예약 반영 — 5박(9/15~9/20) 확정 · 9/15 저녁은 장보기 후 숙소 식사</t>
         </is>
       </c>
     </row>
